--- a/Tools/Excel/Datas/Scene.xlsx
+++ b/Tools/Excel/Datas/Scene.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="24052" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -63,7 +63,10 @@
     <t>scene_res</t>
   </si>
   <si>
-    <t>item_icon</t>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>video</t>
   </si>
   <si>
     <t>##type</t>
@@ -93,13 +96,13 @@
     <t>场景名称</t>
   </si>
   <si>
-    <t>物品描述</t>
-  </si>
-  <si>
-    <t>物品图标</t>
-  </si>
-  <si>
-    <t>主场景</t>
+    <t>场景名字</t>
+  </si>
+  <si>
+    <t>场景图标</t>
+  </si>
+  <si>
+    <t>主场景描述描述</t>
   </si>
   <si>
     <t>场景1</t>
@@ -109,6 +112,54 @@
   </si>
   <si>
     <t>icon_scene_1001</t>
+  </si>
+  <si>
+    <t>vedio_scene_1001</t>
+  </si>
+  <si>
+    <t>场景2描述描述</t>
+  </si>
+  <si>
+    <t>场景2</t>
+  </si>
+  <si>
+    <t>Scene1002</t>
+  </si>
+  <si>
+    <t>icon_scene_1002</t>
+  </si>
+  <si>
+    <t>vedio_scene_1002</t>
+  </si>
+  <si>
+    <t>场景3描述描述</t>
+  </si>
+  <si>
+    <t>场景3</t>
+  </si>
+  <si>
+    <t>Scene1003</t>
+  </si>
+  <si>
+    <t>icon_scene_1003</t>
+  </si>
+  <si>
+    <t>vedio_scene_1003</t>
+  </si>
+  <si>
+    <t>场景4描述描述</t>
+  </si>
+  <si>
+    <t>场景4</t>
+  </si>
+  <si>
+    <t>Scene1004</t>
+  </si>
+  <si>
+    <t>icon_scene_1004</t>
+  </si>
+  <si>
+    <t>vedio_scene_1004</t>
   </si>
 </sst>
 </file>
@@ -1082,17 +1133,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.375" style="3" customWidth="1"/>
-    <col min="4" max="6" width="23.75" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9.24778761061947" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.6283185840708" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.3716814159292" style="3" customWidth="1"/>
+    <col min="4" max="7" width="23.7522123893805" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="13.9" spans="1:7">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1111,8 +1162,11 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1121,82 +1175,155 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:6">
+    <row r="3" s="2" customFormat="1" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:6">
+    <row r="4" s="2" customFormat="1" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="33.95" customHeight="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="33.95" customHeight="1" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:7">
       <c r="B6" s="3">
         <v>1001</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="3">
+        <v>1004</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Tools/Excel/Datas/Scene.xlsx
+++ b/Tools/Excel/Datas/Scene.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -69,6 +69,9 @@
     <t>video</t>
   </si>
   <si>
+    <t>audio</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -102,6 +105,9 @@
     <t>场景图标</t>
   </si>
   <si>
+    <t>声音资源</t>
+  </si>
+  <si>
     <t>主场景描述描述</t>
   </si>
   <si>
@@ -117,6 +123,9 @@
     <t>vedio_scene_1001</t>
   </si>
   <si>
+    <t>music_bg1001</t>
+  </si>
+  <si>
     <t>场景2描述描述</t>
   </si>
   <si>
@@ -132,6 +141,9 @@
     <t>vedio_scene_1002</t>
   </si>
   <si>
+    <t>music_bg1002</t>
+  </si>
+  <si>
     <t>场景3描述描述</t>
   </si>
   <si>
@@ -147,6 +159,9 @@
     <t>vedio_scene_1003</t>
   </si>
   <si>
+    <t>music_bg1003</t>
+  </si>
+  <si>
     <t>场景4描述描述</t>
   </si>
   <si>
@@ -160,6 +175,9 @@
   </si>
   <si>
     <t>vedio_scene_1004</t>
+  </si>
+  <si>
+    <t>music_bg1004</t>
   </si>
 </sst>
 </file>
@@ -1133,17 +1151,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="6"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.6283185840708" style="3" customWidth="1"/>
     <col min="3" max="3" width="21.3716814159292" style="3" customWidth="1"/>
-    <col min="4" max="7" width="23.7522123893805" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="4" max="8" width="23.7522123893805" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13.9" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="13.9" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1165,8 +1183,11 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1176,154 +1197,176 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:7">
+    <row r="3" s="2" customFormat="1" spans="1:8">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:7">
+    <row r="4" s="2" customFormat="1" spans="1:8">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="33.95" customHeight="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="33.95" customHeight="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:8">
       <c r="B6" s="3">
         <v>1001</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:8">
       <c r="B7" s="3">
         <v>1002</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:8">
       <c r="B8" s="3">
         <v>1003</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:8">
       <c r="B9" s="3">
         <v>1004</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
